--- a/webapp/backend/samples/TAKSY_VPM_Landscape_v3.xlsx
+++ b/webapp/backend/samples/TAKSY_VPM_Landscape_v3.xlsx
@@ -9,17 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How_To" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shape_Library" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line_Rules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagrams" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edges" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagrams" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edges" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shape_Library'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Line_Rules'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Diagrams'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Nodes'!$A$1:$K$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Edges'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Diagrams'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Nodes'!$A$1:$K$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Edges'!$A$1:$G$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -548,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -624,194 +622,47 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>group</t>
+          <t>bus_lane</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>Network</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>rectangle, dashed</t>
+          <t>rectangle</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>200</v>
-      </c>
       <c r="G2" s="5" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>#FFFFFF</t>
+          <t>#EAF6FB</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>#808080</t>
+          <t>#4A90B8</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>container</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>Generic container; size from children</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>application_component</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>#DAE8FC</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>#4A7EBB</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>Standard system/module box</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>database</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>cylinder</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>#E1D5E7</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>#9673A6</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Data store</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>bus_lane</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>#EAF6FB</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>#4A90B8</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Wide horizontal integration bus (AIN)</t>
         </is>
@@ -824,185 +675,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>relation_type</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>line_style</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>width_px</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>source_end</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>target_end</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>routing</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>label_position</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>color_hex</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>data_flow</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>open arrow</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>#3B6EA8</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Numbered integration/interface reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>association</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>open arrow</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>#666666</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Generic link</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1089,7 +761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2488,7 +2160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
